--- a/AtchisonRegime/Outputs/Japan/df_regZScores_Japan.xlsx
+++ b/AtchisonRegime/Outputs/Japan/df_regZScores_Japan.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6062,7 +6062,7 @@
         <v>0.2744934912130399</v>
       </c>
       <c r="C331" t="n">
-        <v>0.1143020237392588</v>
+        <v>0.09483981685732353</v>
       </c>
       <c r="D331" t="n">
         <v>0.6607631425232638</v>
@@ -6079,7 +6079,7 @@
         <v>0.247043822107174</v>
       </c>
       <c r="C332" t="n">
-        <v>0.07839956235737192</v>
+        <v>0.02622896941243575</v>
       </c>
       <c r="D332" t="n">
         <v>0.6738196246178002</v>
@@ -6096,7 +6096,7 @@
         <v>0.2764810102827051</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.04075924110783925</v>
+        <v>-0.08493118817654892</v>
       </c>
       <c r="D333" t="n">
         <v>0.64392862120351</v>
@@ -6113,7 +6113,7 @@
         <v>0.2775195757319146</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.1700193597796587</v>
+        <v>-0.1830661174124763</v>
       </c>
       <c r="D334" t="n">
         <v>0.5453937035152667</v>
@@ -6130,7 +6130,7 @@
         <v>0.1358080368870456</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.2210773005275436</v>
+        <v>-0.2048588663815025</v>
       </c>
       <c r="D335" t="n">
         <v>0.4012988812070913</v>
@@ -6147,7 +6147,7 @@
         <v>-0.1011804355610571</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.3207525013009814</v>
+        <v>-0.2269911939414751</v>
       </c>
       <c r="D336" t="n">
         <v>0.2692656463854147</v>
@@ -6164,7 +6164,7 @@
         <v>-0.2269313581600936</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.2836938197787018</v>
+        <v>-0.2150979956911355</v>
       </c>
       <c r="D337" t="n">
         <v>0.2201519689621168</v>
@@ -6181,7 +6181,7 @@
         <v>0.1293460533979883</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.2927346215005262</v>
+        <v>-0.150710709240619</v>
       </c>
       <c r="D338" t="n">
         <v>0.1470370271165108</v>
@@ -6198,7 +6198,7 @@
         <v>0.8294513901668797</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.2023349038685079</v>
+        <v>-0.08552533138729648</v>
       </c>
       <c r="D339" t="n">
         <v>0.1763511896644202</v>
@@ -6215,7 +6215,7 @@
         <v>1.256555449945676</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.1575668569988701</v>
+        <v>-0.07846608629638509</v>
       </c>
       <c r="D340" t="n">
         <v>0.1371594861448566</v>
@@ -6229,16 +6229,33 @@
         <v>45747</v>
       </c>
       <c r="B341" t="n">
-        <v>1.366111373837551</v>
+        <v>1.316054207954405</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.1091321474455471</v>
+        <v>-0.1099834431928019</v>
       </c>
       <c r="D341" t="n">
         <v>0.1110546272241258</v>
       </c>
       <c r="E341" t="n">
         <v>-0.1283410707788303</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B342" t="n">
+        <v>1.008852221221361</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.04018897446938442</v>
+      </c>
+      <c r="D342" t="n">
+        <v>-0.1433469846859853</v>
+      </c>
+      <c r="E342" t="n">
+        <v>-0.2934007498358872</v>
       </c>
     </row>
   </sheetData>
